--- a/daily_matches/job_matches_2026-07-25.xlsx
+++ b/daily_matches/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior MarTech Engineer (Braze/Claude)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Mistral, Prompt Engineering, Cortex, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6359d2f982d74afd</t>
+          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Mistral, Prompt Engineering, Cortex, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Data Lake, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb87927ba32fbcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Data Platform</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Hadoop, R, Java</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Analyst - Forensics, Technology, Investigations &amp; Discovery</t>
+          <t>Sr. Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Berkeley Research Group, LLC</t>
+          <t>Lovesac</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Kubernetes, PySpark, Hadoop, Tableau, Python, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Dataflow, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f2a5ae1f608b5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d666b2674d51e46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer III-Databricks</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, BigQuery, BigQuery, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, TensorFlow, EC2, Kubernetes, CI/CD, Terraform, Databricks, PySpark, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d47d02b727e8313</t>
+          <t>https://www.indeed.com/viewjob?jk=097f3e8cd3b1164b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technology Risk Specialist | Technology Risk Management</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Python, SQL, R, Scala</t>
+          <t>LangChain, Prompt Engineering, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,137 +671,137 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fac7f32fb6b3fa7e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Data Science, Full Time, Days, Monday- Friday 8:30 am-5pm</t>
+          <t>Senior Platform Engineer - Frisco</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jackson Health System</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3789a5858b85a3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=08be12ad175e6a62</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, S3, Docker, Kafka, Hadoop, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d006d0e4098d7f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Junior Data Engineer/Junior Data Scientist</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Docker, Terraform, Git, Polars, Dask</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b283b9657871da6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Junior Data Engineer/Junior Data Scientist</t>
+          <t>Senior IT Developer TDS (US)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Kafka, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c59d1117e59e127</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Trading Systems</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Arrowstreet Capital LP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, S3, EC2, Kubernetes, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c648e269e1e07828</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III NA (Contract Talent)</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ad32a4b56ed3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, BigQuery, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf02a1f591fc67d</t>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, R, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e58a2ea2f0a2da</t>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, R, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ed627fa14be8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Care Innovation - Senior Solution Engineer 135-2034</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CommunityCare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cf92c78d19cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=23652f46d485f93d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>TAIT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lititz, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, S3, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d39b05e71e7c6ae</t>
+          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90299ec4f37a0b8</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>React Web Developer</t>
+          <t>Senior DataOps Engineer ( Remote US)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Git, R, Java, Scala, Optimization</t>
+          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,42 +1126,1547 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2d91e553d7ee3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b9cf29eaf2fb3e62</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack .NET Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Versa Networks</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Jenkins, Terraform, Git, Kafka, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Versa Networks</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Dask, Python</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37b783bdd869d2fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SW Engineer- Developer Systems Reliability Engineering</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Jenkins, Terraform, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4d70957216304f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Associate</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Acentra Health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=310341df3d33c819</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>West Monroe</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Synapse, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer II-Python/PySpark</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Distinguished AI Engineer (Office of the CTO)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, AWS SageMaker, Azure ML, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0b2b5ffa013e942</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr AI Engineer - Advanced AI (ML Ops, LLMs, Agentic workflows)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, LLaMA, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4fe1752aaf513a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Developer II – .NET Full Stack</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RealPage Inc</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=956639042f81c8b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Care Innovation - Senior Solution Architect 136-2001</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CommunityCare</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11dc35d5ff7de121</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>McAfee</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=297c48956109daa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=717414d3718b8dd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Versa Networks</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Matplotlib, Seaborn, Python, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b8d4313764bef26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Prompt Engineering, S3, MLflow, Python, R, Scala, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=900da89c96c1b7ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Scientist Senior Associate</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Glue, Docker, CI/CD, Jenkins, Git, PySpark, Python, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Frontend Leaning)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LeafLink</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41172f20e19b527c</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sr. Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec22d2fe6069bdac</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Engineer, AI Engineering (R5459)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Shield AI</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Git, Snowflake, Databricks, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1760367b04dd084</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Engineer, AI Engineering (R5450)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Shield AI</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Git, Snowflake, Databricks, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2263aa5934d2d20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer II, AI Platform</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5eddaaebb83b7451</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Delan Associates, Inc</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Copilot, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9d58845cd85d78f</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Data Analyst / Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>McAfee</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, PostgreSQL, MongoDB, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Engineer, Generalist in Autonomous Driving System</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Bot Auto</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfc94fcc7aef0bdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineer, Generalist in Autonomous Driving System</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Bot Auto</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d73a1b72f95c4ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer II - Ingestion AI Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Aledade, Inc.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d57b1e30b0790fac</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Security Operations Engineer (Incident Response)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ProCircular</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>North Liberty, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de0931b873850bee</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Product Security Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, FastAPI, Kubernetes, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c9763f7a76f31e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AWS &amp; Databricks Platform Architect</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Docker, Terraform, Databricks, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Care Innovation - Automation Engineer 136-2000</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CommunityCare</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32c2732ef70a8ec8</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer (33139)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pantherx Specialty Llc</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, PySpark, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data Scientist III - FCRM</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d93525645b182736</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da3a17bfc9f9ef67</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eeed71f970ae86f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b86a6e416cb73147</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Delivery Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=877b4b0e854caca3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Delivery Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ddf01b7f2efb719</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Delivery Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92e866c26a5b19a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Brown Brothers Harriman</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7dcfa9ea6235a02</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Science Senior Associate- Card Data &amp; Analytics team</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2376274cfd8a7f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>React Web Developer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
         <v>10</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd91ced7942d1f84</t>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab5a8a0e267df7c7</t>
         </is>
       </c>
     </row>
